--- a/Data/EXCEL/Transfer/salemon/202208/6549-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/6549-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1EBA0F07-D27E-4495-A322-E8087F360862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D0EB108D-4006-4D50-8BF7-53EC8042354F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="6549-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="18">
   <si>
     <t>月別</t>
   </si>
@@ -80,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -261,9 +261,9 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF008000"/>
+      <color rgb="FFFF0000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -271,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF008000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -818,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -845,22 +853,22 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1218,21 +1226,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q89"/>
+  <dimension ref="A1:Q90"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.75" customWidth="1"/>
-    <col min="2" max="5" width="9.875" customWidth="1"/>
-    <col min="6" max="6" width="9.375" customWidth="1"/>
-    <col min="7" max="7" width="10.875" customWidth="1"/>
-    <col min="8" max="8" width="11.25" customWidth="1"/>
-    <col min="9" max="10" width="9.375" customWidth="1"/>
-    <col min="11" max="11" width="9.875" customWidth="1"/>
-    <col min="12" max="12" width="9.375" customWidth="1"/>
-    <col min="13" max="13" width="11.25" customWidth="1"/>
-    <col min="14" max="15" width="9.375" customWidth="1"/>
-    <col min="16" max="16" width="9.875" customWidth="1"/>
-    <col min="17" max="17" width="10.875" customWidth="1"/>
+    <col min="1" max="1" width="16.75" customWidth="1"/>
+    <col min="2" max="5" width="14.125" customWidth="1"/>
+    <col min="6" max="6" width="13.375" customWidth="1"/>
+    <col min="7" max="7" width="15.375" customWidth="1"/>
+    <col min="8" max="8" width="16.125" customWidth="1"/>
+    <col min="9" max="10" width="13.375" customWidth="1"/>
+    <col min="11" max="11" width="14.125" customWidth="1"/>
+    <col min="12" max="12" width="13.375" customWidth="1"/>
+    <col min="13" max="13" width="16.125" customWidth="1"/>
+    <col min="14" max="15" width="13.375" customWidth="1"/>
+    <col min="16" max="17" width="14.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -1385,25 +1392,25 @@
     </row>
     <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>44743</v>
+        <v>44774</v>
       </c>
       <c r="B5" s="7">
-        <v>10.050000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="C5" s="7">
-        <v>9.73</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="D5" s="7">
-        <v>10.050000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="E5" s="7">
-        <v>9</v>
+        <v>8.51</v>
       </c>
       <c r="F5" s="8">
-        <v>-0.32</v>
+        <v>0.47</v>
       </c>
       <c r="G5" s="8">
-        <v>-3.18</v>
+        <v>4.83</v>
       </c>
       <c r="H5" s="9">
         <v>0</v>
@@ -1411,52 +1418,52 @@
       <c r="I5" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="8">
+      <c r="J5" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5" s="9">
+        <v>0</v>
+      </c>
+      <c r="L5" s="10">
         <v>-100</v>
       </c>
-      <c r="K5" s="9">
-        <v>0</v>
-      </c>
-      <c r="L5" s="8">
-        <v>-100</v>
-      </c>
       <c r="M5" s="9">
         <v>0</v>
       </c>
       <c r="N5" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O5" s="8">
-        <v>-100</v>
+      <c r="O5" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P5" s="9">
         <v>0</v>
       </c>
-      <c r="Q5" s="8">
+      <c r="Q5" s="10">
         <v>-100</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>44713</v>
+        <v>44743</v>
       </c>
       <c r="B6" s="7">
-        <v>9.98</v>
+        <v>10.050000000000001</v>
       </c>
       <c r="C6" s="7">
+        <v>9.73</v>
+      </c>
+      <c r="D6" s="7">
         <v>10.050000000000001</v>
       </c>
-      <c r="D6" s="7">
-        <v>10.5</v>
-      </c>
       <c r="E6" s="7">
-        <v>9.51</v>
+        <v>9</v>
       </c>
       <c r="F6" s="10">
-        <v>7.0000000000000007E-2</v>
+        <v>-0.32</v>
       </c>
       <c r="G6" s="10">
-        <v>0.7</v>
+        <v>-3.18</v>
       </c>
       <c r="H6" s="9">
         <v>0</v>
@@ -1464,13 +1471,13 @@
       <c r="I6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="8">
+      <c r="J6" s="10">
         <v>-100</v>
       </c>
       <c r="K6" s="9">
         <v>0</v>
       </c>
-      <c r="L6" s="8">
+      <c r="L6" s="10">
         <v>-100</v>
       </c>
       <c r="M6" s="9">
@@ -1479,37 +1486,37 @@
       <c r="N6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O6" s="8">
+      <c r="O6" s="10">
         <v>-100</v>
       </c>
       <c r="P6" s="9">
         <v>0</v>
       </c>
-      <c r="Q6" s="8">
+      <c r="Q6" s="10">
         <v>-100</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B7" s="7">
-        <v>10.8</v>
+        <v>9.98</v>
       </c>
       <c r="C7" s="7">
-        <v>9.98</v>
+        <v>10.050000000000001</v>
       </c>
       <c r="D7" s="7">
-        <v>10.85</v>
+        <v>10.5</v>
       </c>
       <c r="E7" s="7">
-        <v>9.1999999999999993</v>
+        <v>9.51</v>
       </c>
       <c r="F7" s="8">
-        <v>-0.82</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G7" s="8">
-        <v>-7.59</v>
+        <v>0.7</v>
       </c>
       <c r="H7" s="9">
         <v>0</v>
@@ -1517,13 +1524,13 @@
       <c r="I7" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J7" s="9" t="s">
-        <v>17</v>
+      <c r="J7" s="10">
+        <v>-100</v>
       </c>
       <c r="K7" s="9">
         <v>0</v>
       </c>
-      <c r="L7" s="8">
+      <c r="L7" s="10">
         <v>-100</v>
       </c>
       <c r="M7" s="9">
@@ -1532,37 +1539,37 @@
       <c r="N7" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O7" s="9" t="s">
-        <v>17</v>
+      <c r="O7" s="10">
+        <v>-100</v>
       </c>
       <c r="P7" s="9">
         <v>0</v>
       </c>
-      <c r="Q7" s="8">
+      <c r="Q7" s="10">
         <v>-100</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B8" s="7">
-        <v>11.65</v>
+        <v>10.8</v>
       </c>
       <c r="C8" s="7">
-        <v>10.8</v>
+        <v>9.98</v>
       </c>
       <c r="D8" s="7">
-        <v>11.6</v>
+        <v>10.85</v>
       </c>
       <c r="E8" s="7">
-        <v>10.4</v>
-      </c>
-      <c r="F8" s="8">
-        <v>-0.85</v>
-      </c>
-      <c r="G8" s="8">
-        <v>-7.3</v>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="F8" s="10">
+        <v>-0.82</v>
+      </c>
+      <c r="G8" s="10">
+        <v>-7.59</v>
       </c>
       <c r="H8" s="9">
         <v>0</v>
@@ -1576,7 +1583,7 @@
       <c r="K8" s="9">
         <v>0</v>
       </c>
-      <c r="L8" s="8">
+      <c r="L8" s="10">
         <v>-100</v>
       </c>
       <c r="M8" s="9">
@@ -1591,31 +1598,31 @@
       <c r="P8" s="9">
         <v>0</v>
       </c>
-      <c r="Q8" s="8">
+      <c r="Q8" s="10">
         <v>-100</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B9" s="7">
-        <v>13.15</v>
+        <v>11.65</v>
       </c>
       <c r="C9" s="7">
-        <v>11.65</v>
+        <v>10.8</v>
       </c>
       <c r="D9" s="7">
-        <v>13.4</v>
+        <v>11.6</v>
       </c>
       <c r="E9" s="7">
-        <v>10.8</v>
-      </c>
-      <c r="F9" s="8">
-        <v>-1.5</v>
-      </c>
-      <c r="G9" s="8">
-        <v>-11.41</v>
+        <v>10.4</v>
+      </c>
+      <c r="F9" s="10">
+        <v>-0.85</v>
+      </c>
+      <c r="G9" s="10">
+        <v>-7.3</v>
       </c>
       <c r="H9" s="9">
         <v>0</v>
@@ -1623,52 +1630,52 @@
       <c r="I9" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J9" s="8">
+      <c r="J9" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K9" s="9">
+        <v>0</v>
+      </c>
+      <c r="L9" s="10">
         <v>-100</v>
       </c>
-      <c r="K9" s="9">
-        <v>0</v>
-      </c>
-      <c r="L9" s="8">
-        <v>-100</v>
-      </c>
       <c r="M9" s="9">
         <v>0</v>
       </c>
       <c r="N9" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O9" s="8">
-        <v>-100</v>
+      <c r="O9" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P9" s="9">
         <v>0</v>
       </c>
-      <c r="Q9" s="8">
+      <c r="Q9" s="10">
         <v>-100</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B10" s="7">
-        <v>12.05</v>
+        <v>13.15</v>
       </c>
       <c r="C10" s="7">
-        <v>13.15</v>
+        <v>11.65</v>
       </c>
       <c r="D10" s="7">
-        <v>15</v>
+        <v>13.4</v>
       </c>
       <c r="E10" s="7">
-        <v>12.05</v>
+        <v>10.8</v>
       </c>
       <c r="F10" s="10">
-        <v>1.1000000000000001</v>
+        <v>-1.5</v>
       </c>
       <c r="G10" s="10">
-        <v>9.1300000000000008</v>
+        <v>-11.41</v>
       </c>
       <c r="H10" s="9">
         <v>0</v>
@@ -1676,14 +1683,14 @@
       <c r="I10" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J10" s="9" t="s">
-        <v>17</v>
+      <c r="J10" s="10">
+        <v>-100</v>
       </c>
       <c r="K10" s="9">
         <v>0</v>
       </c>
-      <c r="L10" s="9" t="s">
-        <v>17</v>
+      <c r="L10" s="10">
+        <v>-100</v>
       </c>
       <c r="M10" s="9">
         <v>0</v>
@@ -1691,37 +1698,37 @@
       <c r="N10" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O10" s="9" t="s">
-        <v>17</v>
+      <c r="O10" s="10">
+        <v>-100</v>
       </c>
       <c r="P10" s="9">
         <v>0</v>
       </c>
-      <c r="Q10" s="9" t="s">
-        <v>17</v>
+      <c r="Q10" s="10">
+        <v>-100</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B11" s="7">
-        <v>10.1</v>
+        <v>12.05</v>
       </c>
       <c r="C11" s="7">
+        <v>13.15</v>
+      </c>
+      <c r="D11" s="7">
+        <v>15</v>
+      </c>
+      <c r="E11" s="7">
         <v>12.05</v>
       </c>
-      <c r="D11" s="7">
-        <v>14.35</v>
-      </c>
-      <c r="E11" s="7">
-        <v>9.92</v>
-      </c>
-      <c r="F11" s="10">
-        <v>1.95</v>
-      </c>
-      <c r="G11" s="10">
-        <v>19.309999999999999</v>
+      <c r="F11" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G11" s="8">
+        <v>9.1300000000000008</v>
       </c>
       <c r="H11" s="9">
         <v>0</v>
@@ -1756,25 +1763,25 @@
     </row>
     <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B12" s="7">
-        <v>9.16</v>
+        <v>10.1</v>
       </c>
       <c r="C12" s="7">
-        <v>10.1</v>
+        <v>12.05</v>
       </c>
       <c r="D12" s="7">
-        <v>11.15</v>
+        <v>14.35</v>
       </c>
       <c r="E12" s="7">
-        <v>9.1</v>
-      </c>
-      <c r="F12" s="10">
-        <v>0.94</v>
-      </c>
-      <c r="G12" s="10">
-        <v>10.26</v>
+        <v>9.92</v>
+      </c>
+      <c r="F12" s="8">
+        <v>1.95</v>
+      </c>
+      <c r="G12" s="8">
+        <v>19.309999999999999</v>
       </c>
       <c r="H12" s="9">
         <v>0</v>
@@ -1786,7 +1793,7 @@
         <v>17</v>
       </c>
       <c r="K12" s="9">
-        <v>0.221</v>
+        <v>0</v>
       </c>
       <c r="L12" s="9" t="s">
         <v>17</v>
@@ -1801,7 +1808,7 @@
         <v>17</v>
       </c>
       <c r="P12" s="9">
-        <v>0.221</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="9" t="s">
         <v>17</v>
@@ -1809,31 +1816,31 @@
     </row>
     <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B13" s="7">
-        <v>10.199999999999999</v>
+        <v>9.16</v>
       </c>
       <c r="C13" s="7">
-        <v>9.16</v>
+        <v>10.1</v>
       </c>
       <c r="D13" s="7">
-        <v>10.3</v>
+        <v>11.15</v>
       </c>
       <c r="E13" s="7">
-        <v>9.07</v>
+        <v>9.1</v>
       </c>
       <c r="F13" s="8">
-        <v>-1.04</v>
+        <v>0.94</v>
       </c>
       <c r="G13" s="8">
-        <v>-10.199999999999999</v>
+        <v>10.26</v>
       </c>
       <c r="H13" s="9">
         <v>0</v>
       </c>
-      <c r="I13" s="8">
-        <v>-100</v>
+      <c r="I13" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J13" s="9" t="s">
         <v>17</v>
@@ -1847,8 +1854,8 @@
       <c r="M13" s="9">
         <v>0</v>
       </c>
-      <c r="N13" s="8">
-        <v>-100</v>
+      <c r="N13" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O13" s="9" t="s">
         <v>17</v>
@@ -1862,31 +1869,31 @@
     </row>
     <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B14" s="7">
-        <v>11.1</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="C14" s="7">
-        <v>10.199999999999999</v>
+        <v>9.16</v>
       </c>
       <c r="D14" s="7">
-        <v>11.1</v>
+        <v>10.3</v>
       </c>
       <c r="E14" s="7">
-        <v>9.9</v>
-      </c>
-      <c r="F14" s="8">
-        <v>-0.9</v>
-      </c>
-      <c r="G14" s="8">
-        <v>-8.11</v>
+        <v>9.07</v>
+      </c>
+      <c r="F14" s="10">
+        <v>-1.04</v>
+      </c>
+      <c r="G14" s="10">
+        <v>-10.199999999999999</v>
       </c>
       <c r="H14" s="9">
-        <v>2.5000000000000001E-3</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="I14" s="10">
+        <v>-100</v>
       </c>
       <c r="J14" s="9" t="s">
         <v>17</v>
@@ -1898,10 +1905,10 @@
         <v>17</v>
       </c>
       <c r="M14" s="9">
-        <v>2.5000000000000001E-3</v>
-      </c>
-      <c r="N14" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="N14" s="10">
+        <v>-100</v>
       </c>
       <c r="O14" s="9" t="s">
         <v>17</v>
@@ -1915,28 +1922,28 @@
     </row>
     <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B15" s="7">
-        <v>10.15</v>
+        <v>11.1</v>
       </c>
       <c r="C15" s="7">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="D15" s="7">
         <v>11.1</v>
       </c>
-      <c r="D15" s="7">
-        <v>12.1</v>
-      </c>
       <c r="E15" s="7">
-        <v>10.050000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="F15" s="10">
-        <v>0.95</v>
+        <v>-0.9</v>
       </c>
       <c r="G15" s="10">
-        <v>9.36</v>
+        <v>-8.11</v>
       </c>
       <c r="H15" s="9">
-        <v>0</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="I15" s="9" t="s">
         <v>17</v>
@@ -1945,13 +1952,13 @@
         <v>17</v>
       </c>
       <c r="K15" s="9">
-        <v>0.218</v>
+        <v>0.221</v>
       </c>
       <c r="L15" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M15" s="9">
-        <v>0</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="N15" s="9" t="s">
         <v>17</v>
@@ -1960,7 +1967,7 @@
         <v>17</v>
       </c>
       <c r="P15" s="9">
-        <v>0.218</v>
+        <v>0.221</v>
       </c>
       <c r="Q15" s="9" t="s">
         <v>17</v>
@@ -1968,31 +1975,31 @@
     </row>
     <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B16" s="7">
-        <v>11.15</v>
+        <v>10.15</v>
       </c>
       <c r="C16" s="7">
-        <v>10.15</v>
+        <v>11.1</v>
       </c>
       <c r="D16" s="7">
-        <v>11.3</v>
+        <v>12.1</v>
       </c>
       <c r="E16" s="7">
-        <v>9.61</v>
+        <v>10.050000000000001</v>
       </c>
       <c r="F16" s="8">
-        <v>-1</v>
+        <v>0.95</v>
       </c>
       <c r="G16" s="8">
-        <v>-8.9700000000000006</v>
+        <v>9.36</v>
       </c>
       <c r="H16" s="9">
         <v>0</v>
       </c>
-      <c r="I16" s="8">
-        <v>-100</v>
+      <c r="I16" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J16" s="9" t="s">
         <v>17</v>
@@ -2006,8 +2013,8 @@
       <c r="M16" s="9">
         <v>0</v>
       </c>
-      <c r="N16" s="8">
-        <v>-100</v>
+      <c r="N16" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O16" s="9" t="s">
         <v>17</v>
@@ -2021,31 +2028,31 @@
     </row>
     <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B17" s="7">
-        <v>12.75</v>
+        <v>11.15</v>
       </c>
       <c r="C17" s="7">
-        <v>11.15</v>
+        <v>10.15</v>
       </c>
       <c r="D17" s="7">
-        <v>13.05</v>
+        <v>11.3</v>
       </c>
       <c r="E17" s="7">
-        <v>10.75</v>
-      </c>
-      <c r="F17" s="8">
-        <v>-1.6</v>
-      </c>
-      <c r="G17" s="8">
-        <v>-12.55</v>
+        <v>9.61</v>
+      </c>
+      <c r="F17" s="10">
+        <v>-1</v>
+      </c>
+      <c r="G17" s="10">
+        <v>-8.9700000000000006</v>
       </c>
       <c r="H17" s="9">
-        <v>2.5000000000000001E-3</v>
-      </c>
-      <c r="I17" s="8">
-        <v>-50</v>
+        <v>0</v>
+      </c>
+      <c r="I17" s="10">
+        <v>-100</v>
       </c>
       <c r="J17" s="9" t="s">
         <v>17</v>
@@ -2057,10 +2064,10 @@
         <v>17</v>
       </c>
       <c r="M17" s="9">
-        <v>2.5000000000000001E-3</v>
-      </c>
-      <c r="N17" s="8">
-        <v>-50</v>
+        <v>0</v>
+      </c>
+      <c r="N17" s="10">
+        <v>-100</v>
       </c>
       <c r="O17" s="9" t="s">
         <v>17</v>
@@ -2074,52 +2081,52 @@
     </row>
     <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B18" s="7">
-        <v>14.25</v>
+        <v>12.75</v>
       </c>
       <c r="C18" s="7">
-        <v>12.75</v>
+        <v>11.15</v>
       </c>
       <c r="D18" s="7">
-        <v>14.25</v>
+        <v>13.05</v>
       </c>
       <c r="E18" s="7">
-        <v>12.45</v>
-      </c>
-      <c r="F18" s="8">
-        <v>-1.5</v>
-      </c>
-      <c r="G18" s="8">
-        <v>-10.53</v>
+        <v>10.75</v>
+      </c>
+      <c r="F18" s="10">
+        <v>-1.6</v>
+      </c>
+      <c r="G18" s="10">
+        <v>-12.55</v>
       </c>
       <c r="H18" s="9">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="I18" s="9" t="s">
-        <v>17</v>
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="I18" s="10">
+        <v>-50</v>
       </c>
       <c r="J18" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K18" s="9">
-        <v>0.216</v>
+        <v>0.218</v>
       </c>
       <c r="L18" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M18" s="9">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="N18" s="9" t="s">
-        <v>17</v>
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="N18" s="10">
+        <v>-50</v>
       </c>
       <c r="O18" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P18" s="9">
-        <v>0.216</v>
+        <v>0.218</v>
       </c>
       <c r="Q18" s="9" t="s">
         <v>17</v>
@@ -2127,28 +2134,28 @@
     </row>
     <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B19" s="7">
-        <v>14.3</v>
+        <v>14.25</v>
       </c>
       <c r="C19" s="7">
+        <v>12.75</v>
+      </c>
+      <c r="D19" s="7">
         <v>14.25</v>
       </c>
-      <c r="D19" s="7">
-        <v>14.55</v>
-      </c>
       <c r="E19" s="7">
-        <v>12.4</v>
-      </c>
-      <c r="F19" s="8">
-        <v>-0.05</v>
-      </c>
-      <c r="G19" s="8">
-        <v>-0.35</v>
+        <v>12.45</v>
+      </c>
+      <c r="F19" s="10">
+        <v>-1.5</v>
+      </c>
+      <c r="G19" s="10">
+        <v>-10.53</v>
       </c>
       <c r="H19" s="9">
-        <v>0</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="I19" s="9" t="s">
         <v>17</v>
@@ -2157,13 +2164,13 @@
         <v>17</v>
       </c>
       <c r="K19" s="9">
-        <v>0.21099999999999999</v>
+        <v>0.216</v>
       </c>
       <c r="L19" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M19" s="9">
-        <v>0</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="N19" s="9" t="s">
         <v>17</v>
@@ -2172,7 +2179,7 @@
         <v>17</v>
       </c>
       <c r="P19" s="9">
-        <v>0.21099999999999999</v>
+        <v>0.216</v>
       </c>
       <c r="Q19" s="9" t="s">
         <v>17</v>
@@ -2180,31 +2187,31 @@
     </row>
     <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B20" s="7">
-        <v>14.85</v>
+        <v>14.3</v>
       </c>
       <c r="C20" s="7">
-        <v>14.3</v>
+        <v>14.25</v>
       </c>
       <c r="D20" s="7">
-        <v>15.85</v>
+        <v>14.55</v>
       </c>
       <c r="E20" s="7">
-        <v>14.05</v>
-      </c>
-      <c r="F20" s="8">
-        <v>-0.55000000000000004</v>
-      </c>
-      <c r="G20" s="8">
-        <v>-3.7</v>
+        <v>12.4</v>
+      </c>
+      <c r="F20" s="10">
+        <v>-0.05</v>
+      </c>
+      <c r="G20" s="10">
+        <v>-0.35</v>
       </c>
       <c r="H20" s="9">
         <v>0</v>
       </c>
-      <c r="I20" s="8">
-        <v>-100</v>
+      <c r="I20" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J20" s="9" t="s">
         <v>17</v>
@@ -2218,8 +2225,8 @@
       <c r="M20" s="9">
         <v>0</v>
       </c>
-      <c r="N20" s="8">
-        <v>-100</v>
+      <c r="N20" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O20" s="9" t="s">
         <v>17</v>
@@ -2233,31 +2240,31 @@
     </row>
     <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B21" s="7">
-        <v>14.7</v>
+        <v>14.85</v>
       </c>
       <c r="C21" s="7">
-        <v>14.85</v>
+        <v>14.3</v>
       </c>
       <c r="D21" s="7">
-        <v>16.75</v>
+        <v>15.85</v>
       </c>
       <c r="E21" s="7">
-        <v>14.25</v>
+        <v>14.05</v>
       </c>
       <c r="F21" s="10">
-        <v>0.15</v>
+        <v>-0.55000000000000004</v>
       </c>
       <c r="G21" s="10">
-        <v>1.02</v>
+        <v>-3.7</v>
       </c>
       <c r="H21" s="9">
-        <v>0.21099999999999999</v>
-      </c>
-      <c r="I21" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="I21" s="10">
+        <v>-100</v>
       </c>
       <c r="J21" s="9" t="s">
         <v>17</v>
@@ -2269,10 +2276,10 @@
         <v>17</v>
       </c>
       <c r="M21" s="9">
-        <v>0.21099999999999999</v>
-      </c>
-      <c r="N21" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="N21" s="10">
+        <v>-100</v>
       </c>
       <c r="O21" s="9" t="s">
         <v>17</v>
@@ -2286,28 +2293,28 @@
     </row>
     <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B22" s="7">
-        <v>13.8</v>
+        <v>14.7</v>
       </c>
       <c r="C22" s="7">
-        <v>14.7</v>
+        <v>14.85</v>
       </c>
       <c r="D22" s="7">
-        <v>15.1</v>
+        <v>16.75</v>
       </c>
       <c r="E22" s="7">
-        <v>13.45</v>
-      </c>
-      <c r="F22" s="10">
-        <v>0.9</v>
-      </c>
-      <c r="G22" s="10">
-        <v>6.52</v>
+        <v>14.25</v>
+      </c>
+      <c r="F22" s="8">
+        <v>0.15</v>
+      </c>
+      <c r="G22" s="8">
+        <v>1.02</v>
       </c>
       <c r="H22" s="9">
-        <v>0</v>
+        <v>0.21099999999999999</v>
       </c>
       <c r="I22" s="9" t="s">
         <v>17</v>
@@ -2316,13 +2323,13 @@
         <v>17</v>
       </c>
       <c r="K22" s="9">
-        <v>0</v>
+        <v>0.21099999999999999</v>
       </c>
       <c r="L22" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M22" s="9">
-        <v>0</v>
+        <v>0.21099999999999999</v>
       </c>
       <c r="N22" s="9" t="s">
         <v>17</v>
@@ -2331,7 +2338,7 @@
         <v>17</v>
       </c>
       <c r="P22" s="9">
-        <v>0</v>
+        <v>0.21099999999999999</v>
       </c>
       <c r="Q22" s="9" t="s">
         <v>17</v>
@@ -2339,25 +2346,25 @@
     </row>
     <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B23" s="7">
-        <v>13.35</v>
+        <v>13.8</v>
       </c>
       <c r="C23" s="7">
-        <v>13.8</v>
+        <v>14.7</v>
       </c>
       <c r="D23" s="7">
-        <v>16.850000000000001</v>
+        <v>15.1</v>
       </c>
       <c r="E23" s="7">
-        <v>12.75</v>
-      </c>
-      <c r="F23" s="10">
-        <v>0.45</v>
-      </c>
-      <c r="G23" s="10">
-        <v>3.37</v>
+        <v>13.45</v>
+      </c>
+      <c r="F23" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="G23" s="8">
+        <v>6.52</v>
       </c>
       <c r="H23" s="9">
         <v>0</v>
@@ -2392,25 +2399,25 @@
     </row>
     <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>44166</v>
+        <v>44197</v>
       </c>
       <c r="B24" s="7">
-        <v>14</v>
+        <v>13.35</v>
       </c>
       <c r="C24" s="7">
-        <v>13.35</v>
+        <v>13.8</v>
       </c>
       <c r="D24" s="7">
-        <v>14.05</v>
+        <v>16.850000000000001</v>
       </c>
       <c r="E24" s="7">
-        <v>12.35</v>
+        <v>12.75</v>
       </c>
       <c r="F24" s="8">
-        <v>-0.65</v>
+        <v>0.45</v>
       </c>
       <c r="G24" s="8">
-        <v>-4.6399999999999997</v>
+        <v>3.37</v>
       </c>
       <c r="H24" s="9">
         <v>0</v>
@@ -2424,8 +2431,8 @@
       <c r="K24" s="9">
         <v>0</v>
       </c>
-      <c r="L24" s="8">
-        <v>-100</v>
+      <c r="L24" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="M24" s="9">
         <v>0</v>
@@ -2439,31 +2446,31 @@
       <c r="P24" s="9">
         <v>0</v>
       </c>
-      <c r="Q24" s="8">
-        <v>-100</v>
+      <c r="Q24" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <v>44136</v>
+        <v>44166</v>
       </c>
       <c r="B25" s="7">
-        <v>12.7</v>
+        <v>14</v>
       </c>
       <c r="C25" s="7">
-        <v>14</v>
+        <v>13.35</v>
       </c>
       <c r="D25" s="7">
-        <v>14.7</v>
+        <v>14.05</v>
       </c>
       <c r="E25" s="7">
-        <v>12.45</v>
+        <v>12.35</v>
       </c>
       <c r="F25" s="10">
-        <v>1.3</v>
+        <v>-0.65</v>
       </c>
       <c r="G25" s="10">
-        <v>10.24</v>
+        <v>-4.6399999999999997</v>
       </c>
       <c r="H25" s="9">
         <v>0</v>
@@ -2477,7 +2484,7 @@
       <c r="K25" s="9">
         <v>0</v>
       </c>
-      <c r="L25" s="8">
+      <c r="L25" s="10">
         <v>-100</v>
       </c>
       <c r="M25" s="9">
@@ -2492,31 +2499,31 @@
       <c r="P25" s="9">
         <v>0</v>
       </c>
-      <c r="Q25" s="8">
+      <c r="Q25" s="10">
         <v>-100</v>
       </c>
     </row>
     <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <v>44105</v>
+        <v>44136</v>
       </c>
       <c r="B26" s="7">
-        <v>12.25</v>
+        <v>12.7</v>
       </c>
       <c r="C26" s="7">
-        <v>12.7</v>
+        <v>14</v>
       </c>
       <c r="D26" s="7">
-        <v>15.6</v>
+        <v>14.7</v>
       </c>
       <c r="E26" s="7">
-        <v>12.15</v>
-      </c>
-      <c r="F26" s="10">
-        <v>0.45</v>
-      </c>
-      <c r="G26" s="10">
-        <v>3.67</v>
+        <v>12.45</v>
+      </c>
+      <c r="F26" s="8">
+        <v>1.3</v>
+      </c>
+      <c r="G26" s="8">
+        <v>10.24</v>
       </c>
       <c r="H26" s="9">
         <v>0</v>
@@ -2530,7 +2537,7 @@
       <c r="K26" s="9">
         <v>0</v>
       </c>
-      <c r="L26" s="8">
+      <c r="L26" s="10">
         <v>-100</v>
       </c>
       <c r="M26" s="9">
@@ -2545,31 +2552,31 @@
       <c r="P26" s="9">
         <v>0</v>
       </c>
-      <c r="Q26" s="8">
+      <c r="Q26" s="10">
         <v>-100</v>
       </c>
     </row>
     <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <v>44075</v>
+        <v>44105</v>
       </c>
       <c r="B27" s="7">
-        <v>14.35</v>
+        <v>12.25</v>
       </c>
       <c r="C27" s="7">
-        <v>12.25</v>
+        <v>12.7</v>
       </c>
       <c r="D27" s="7">
-        <v>14.65</v>
+        <v>15.6</v>
       </c>
       <c r="E27" s="7">
-        <v>11.65</v>
+        <v>12.15</v>
       </c>
       <c r="F27" s="8">
-        <v>-2.1</v>
+        <v>0.45</v>
       </c>
       <c r="G27" s="8">
-        <v>-14.63</v>
+        <v>3.67</v>
       </c>
       <c r="H27" s="9">
         <v>0</v>
@@ -2583,7 +2590,7 @@
       <c r="K27" s="9">
         <v>0</v>
       </c>
-      <c r="L27" s="8">
+      <c r="L27" s="10">
         <v>-100</v>
       </c>
       <c r="M27" s="9">
@@ -2598,31 +2605,31 @@
       <c r="P27" s="9">
         <v>0</v>
       </c>
-      <c r="Q27" s="8">
+      <c r="Q27" s="10">
         <v>-100</v>
       </c>
     </row>
     <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
-        <v>44044</v>
+        <v>44075</v>
       </c>
       <c r="B28" s="7">
-        <v>14.95</v>
+        <v>14.35</v>
       </c>
       <c r="C28" s="7">
-        <v>14.35</v>
+        <v>12.25</v>
       </c>
       <c r="D28" s="7">
-        <v>15.7</v>
+        <v>14.65</v>
       </c>
       <c r="E28" s="7">
-        <v>12.55</v>
-      </c>
-      <c r="F28" s="8">
-        <v>-0.6</v>
-      </c>
-      <c r="G28" s="8">
-        <v>-4.01</v>
+        <v>11.65</v>
+      </c>
+      <c r="F28" s="10">
+        <v>-2.1</v>
+      </c>
+      <c r="G28" s="10">
+        <v>-14.63</v>
       </c>
       <c r="H28" s="9">
         <v>0</v>
@@ -2636,7 +2643,7 @@
       <c r="K28" s="9">
         <v>0</v>
       </c>
-      <c r="L28" s="8">
+      <c r="L28" s="10">
         <v>-100</v>
       </c>
       <c r="M28" s="9">
@@ -2651,31 +2658,31 @@
       <c r="P28" s="9">
         <v>0</v>
       </c>
-      <c r="Q28" s="8">
+      <c r="Q28" s="10">
         <v>-100</v>
       </c>
     </row>
     <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
-        <v>44013</v>
+        <v>44044</v>
       </c>
       <c r="B29" s="7">
-        <v>10.6</v>
+        <v>14.95</v>
       </c>
       <c r="C29" s="7">
-        <v>14.95</v>
+        <v>14.35</v>
       </c>
       <c r="D29" s="7">
-        <v>18.850000000000001</v>
+        <v>15.7</v>
       </c>
       <c r="E29" s="7">
-        <v>10.050000000000001</v>
+        <v>12.55</v>
       </c>
       <c r="F29" s="10">
-        <v>4.3499999999999996</v>
+        <v>-0.6</v>
       </c>
       <c r="G29" s="10">
-        <v>41.04</v>
+        <v>-4.01</v>
       </c>
       <c r="H29" s="9">
         <v>0</v>
@@ -2689,7 +2696,7 @@
       <c r="K29" s="9">
         <v>0</v>
       </c>
-      <c r="L29" s="8">
+      <c r="L29" s="10">
         <v>-100</v>
       </c>
       <c r="M29" s="9">
@@ -2704,31 +2711,31 @@
       <c r="P29" s="9">
         <v>0</v>
       </c>
-      <c r="Q29" s="8">
+      <c r="Q29" s="10">
         <v>-100</v>
       </c>
     </row>
     <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
-        <v>43983</v>
+        <v>44013</v>
       </c>
       <c r="B30" s="7">
-        <v>10.35</v>
+        <v>10.6</v>
       </c>
       <c r="C30" s="7">
-        <v>10.6</v>
+        <v>14.95</v>
       </c>
       <c r="D30" s="7">
-        <v>12.25</v>
+        <v>18.850000000000001</v>
       </c>
       <c r="E30" s="7">
-        <v>9.41</v>
-      </c>
-      <c r="F30" s="10">
-        <v>0.25</v>
-      </c>
-      <c r="G30" s="10">
-        <v>2.42</v>
+        <v>10.050000000000001</v>
+      </c>
+      <c r="F30" s="8">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="G30" s="8">
+        <v>41.04</v>
       </c>
       <c r="H30" s="9">
         <v>0</v>
@@ -2742,7 +2749,7 @@
       <c r="K30" s="9">
         <v>0</v>
       </c>
-      <c r="L30" s="8">
+      <c r="L30" s="10">
         <v>-100</v>
       </c>
       <c r="M30" s="9">
@@ -2757,31 +2764,31 @@
       <c r="P30" s="9">
         <v>0</v>
       </c>
-      <c r="Q30" s="8">
+      <c r="Q30" s="10">
         <v>-100</v>
       </c>
     </row>
     <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
-        <v>43952</v>
+        <v>43983</v>
       </c>
       <c r="B31" s="7">
-        <v>9.93</v>
+        <v>10.35</v>
       </c>
       <c r="C31" s="7">
-        <v>10.35</v>
+        <v>10.6</v>
       </c>
       <c r="D31" s="7">
-        <v>13.4</v>
+        <v>12.25</v>
       </c>
       <c r="E31" s="7">
-        <v>8.31</v>
-      </c>
-      <c r="F31" s="10">
-        <v>0.42</v>
-      </c>
-      <c r="G31" s="10">
-        <v>4.2300000000000004</v>
+        <v>9.41</v>
+      </c>
+      <c r="F31" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="G31" s="8">
+        <v>2.42</v>
       </c>
       <c r="H31" s="9">
         <v>0</v>
@@ -2795,7 +2802,7 @@
       <c r="K31" s="9">
         <v>0</v>
       </c>
-      <c r="L31" s="8">
+      <c r="L31" s="10">
         <v>-100</v>
       </c>
       <c r="M31" s="9">
@@ -2810,31 +2817,31 @@
       <c r="P31" s="9">
         <v>0</v>
       </c>
-      <c r="Q31" s="8">
+      <c r="Q31" s="10">
         <v>-100</v>
       </c>
     </row>
     <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
-        <v>43922</v>
+        <v>43952</v>
       </c>
       <c r="B32" s="7">
-        <v>8</v>
+        <v>9.93</v>
       </c>
       <c r="C32" s="7">
-        <v>9.93</v>
+        <v>10.35</v>
       </c>
       <c r="D32" s="7">
-        <v>10.3</v>
+        <v>13.4</v>
       </c>
       <c r="E32" s="7">
-        <v>7.61</v>
-      </c>
-      <c r="F32" s="10">
-        <v>1.93</v>
-      </c>
-      <c r="G32" s="10">
-        <v>24.12</v>
+        <v>8.31</v>
+      </c>
+      <c r="F32" s="8">
+        <v>0.42</v>
+      </c>
+      <c r="G32" s="8">
+        <v>4.2300000000000004</v>
       </c>
       <c r="H32" s="9">
         <v>0</v>
@@ -2842,52 +2849,52 @@
       <c r="I32" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J32" s="8">
+      <c r="J32" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K32" s="9">
+        <v>0</v>
+      </c>
+      <c r="L32" s="10">
         <v>-100</v>
       </c>
-      <c r="K32" s="9">
-        <v>0</v>
-      </c>
-      <c r="L32" s="8">
-        <v>-100</v>
-      </c>
       <c r="M32" s="9">
         <v>0</v>
       </c>
       <c r="N32" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O32" s="8">
-        <v>-100</v>
+      <c r="O32" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P32" s="9">
         <v>0</v>
       </c>
-      <c r="Q32" s="8">
+      <c r="Q32" s="10">
         <v>-100</v>
       </c>
     </row>
     <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
-        <v>43891</v>
+        <v>43922</v>
       </c>
       <c r="B33" s="7">
-        <v>11.41</v>
+        <v>8</v>
       </c>
       <c r="C33" s="7">
-        <v>8</v>
+        <v>9.93</v>
       </c>
       <c r="D33" s="7">
-        <v>11.99</v>
+        <v>10.3</v>
       </c>
       <c r="E33" s="7">
-        <v>5.51</v>
+        <v>7.61</v>
       </c>
       <c r="F33" s="8">
-        <v>-3.41</v>
+        <v>1.93</v>
       </c>
       <c r="G33" s="8">
-        <v>-29.89</v>
+        <v>24.12</v>
       </c>
       <c r="H33" s="9">
         <v>0</v>
@@ -2895,14 +2902,14 @@
       <c r="I33" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J33" s="9" t="s">
-        <v>17</v>
+      <c r="J33" s="10">
+        <v>-100</v>
       </c>
       <c r="K33" s="9">
         <v>0</v>
       </c>
-      <c r="L33" s="9" t="s">
-        <v>17</v>
+      <c r="L33" s="10">
+        <v>-100</v>
       </c>
       <c r="M33" s="9">
         <v>0</v>
@@ -2910,37 +2917,37 @@
       <c r="N33" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O33" s="9" t="s">
-        <v>17</v>
+      <c r="O33" s="10">
+        <v>-100</v>
       </c>
       <c r="P33" s="9">
         <v>0</v>
       </c>
-      <c r="Q33" s="9" t="s">
-        <v>17</v>
+      <c r="Q33" s="10">
+        <v>-100</v>
       </c>
     </row>
     <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
-        <v>43862</v>
+        <v>43891</v>
       </c>
       <c r="B34" s="7">
-        <v>9.8800000000000008</v>
+        <v>11.41</v>
       </c>
       <c r="C34" s="7">
-        <v>11.41</v>
+        <v>8</v>
       </c>
       <c r="D34" s="7">
-        <v>12.3</v>
+        <v>11.99</v>
       </c>
       <c r="E34" s="7">
-        <v>9</v>
+        <v>5.51</v>
       </c>
       <c r="F34" s="10">
-        <v>1.53</v>
+        <v>-3.41</v>
       </c>
       <c r="G34" s="10">
-        <v>15.49</v>
+        <v>-29.89</v>
       </c>
       <c r="H34" s="9">
         <v>0</v>
@@ -2975,25 +2982,25 @@
     </row>
     <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
-        <v>43831</v>
+        <v>43862</v>
       </c>
       <c r="B35" s="7">
-        <v>11.63</v>
+        <v>9.8800000000000008</v>
       </c>
       <c r="C35" s="7">
-        <v>9.8800000000000008</v>
+        <v>11.41</v>
       </c>
       <c r="D35" s="7">
-        <v>13.26</v>
+        <v>12.3</v>
       </c>
       <c r="E35" s="7">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="F35" s="8">
-        <v>-1.75</v>
+        <v>1.53</v>
       </c>
       <c r="G35" s="8">
-        <v>-15.05</v>
+        <v>15.49</v>
       </c>
       <c r="H35" s="9">
         <v>0</v>
@@ -3028,25 +3035,25 @@
     </row>
     <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
-        <v>43800</v>
+        <v>43831</v>
       </c>
       <c r="B36" s="7">
-        <v>10.6</v>
+        <v>11.63</v>
       </c>
       <c r="C36" s="7">
-        <v>11.63</v>
+        <v>9.8800000000000008</v>
       </c>
       <c r="D36" s="7">
-        <v>11.8</v>
+        <v>13.26</v>
       </c>
       <c r="E36" s="7">
-        <v>9.8000000000000007</v>
+        <v>9.4</v>
       </c>
       <c r="F36" s="10">
-        <v>1.03</v>
+        <v>-1.75</v>
       </c>
       <c r="G36" s="10">
-        <v>9.7200000000000006</v>
+        <v>-15.05</v>
       </c>
       <c r="H36" s="9">
         <v>0</v>
@@ -3058,7 +3065,7 @@
         <v>17</v>
       </c>
       <c r="K36" s="9">
-        <v>0.61699999999999999</v>
+        <v>0</v>
       </c>
       <c r="L36" s="9" t="s">
         <v>17</v>
@@ -3073,7 +3080,7 @@
         <v>17</v>
       </c>
       <c r="P36" s="9">
-        <v>0.61699999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q36" s="9" t="s">
         <v>17</v>
@@ -3081,25 +3088,25 @@
     </row>
     <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
-        <v>43770</v>
+        <v>43800</v>
       </c>
       <c r="B37" s="7">
-        <v>11.55</v>
+        <v>10.6</v>
       </c>
       <c r="C37" s="7">
-        <v>10.6</v>
+        <v>11.63</v>
       </c>
       <c r="D37" s="7">
-        <v>12.09</v>
+        <v>11.8</v>
       </c>
       <c r="E37" s="7">
-        <v>9.31</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="F37" s="8">
-        <v>-0.95</v>
+        <v>1.03</v>
       </c>
       <c r="G37" s="8">
-        <v>-8.23</v>
+        <v>9.7200000000000006</v>
       </c>
       <c r="H37" s="9">
         <v>0</v>
@@ -3134,25 +3141,25 @@
     </row>
     <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
-        <v>43739</v>
+        <v>43770</v>
       </c>
       <c r="B38" s="7">
-        <v>9.3000000000000007</v>
+        <v>11.55</v>
       </c>
       <c r="C38" s="7">
-        <v>11.55</v>
+        <v>10.6</v>
       </c>
       <c r="D38" s="7">
-        <v>12.3</v>
+        <v>12.09</v>
       </c>
       <c r="E38" s="7">
-        <v>8.6</v>
+        <v>9.31</v>
       </c>
       <c r="F38" s="10">
-        <v>2.25</v>
+        <v>-0.95</v>
       </c>
       <c r="G38" s="10">
-        <v>24.19</v>
+        <v>-8.23</v>
       </c>
       <c r="H38" s="9">
         <v>0</v>
@@ -3187,25 +3194,25 @@
     </row>
     <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
-        <v>43709</v>
+        <v>43739</v>
       </c>
       <c r="B39" s="7">
-        <v>9.9700000000000006</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="C39" s="7">
-        <v>9.3000000000000007</v>
+        <v>11.55</v>
       </c>
       <c r="D39" s="7">
-        <v>10.09</v>
+        <v>12.3</v>
       </c>
       <c r="E39" s="7">
-        <v>9.1999999999999993</v>
+        <v>8.6</v>
       </c>
       <c r="F39" s="8">
-        <v>-0.67</v>
+        <v>2.25</v>
       </c>
       <c r="G39" s="8">
-        <v>-6.72</v>
+        <v>24.19</v>
       </c>
       <c r="H39" s="9">
         <v>0</v>
@@ -3240,25 +3247,25 @@
     </row>
     <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
-        <v>43678</v>
+        <v>43709</v>
       </c>
       <c r="B40" s="7">
-        <v>12.4</v>
+        <v>9.9700000000000006</v>
       </c>
       <c r="C40" s="7">
-        <v>9.9700000000000006</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="D40" s="7">
-        <v>12.62</v>
+        <v>10.09</v>
       </c>
       <c r="E40" s="7">
-        <v>9.7100000000000009</v>
-      </c>
-      <c r="F40" s="8">
-        <v>-2.4300000000000002</v>
-      </c>
-      <c r="G40" s="8">
-        <v>-19.600000000000001</v>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="F40" s="10">
+        <v>-0.67</v>
+      </c>
+      <c r="G40" s="10">
+        <v>-6.72</v>
       </c>
       <c r="H40" s="9">
         <v>0</v>
@@ -3293,25 +3300,25 @@
     </row>
     <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
-        <v>43647</v>
+        <v>43678</v>
       </c>
       <c r="B41" s="7">
-        <v>10.1</v>
+        <v>12.4</v>
       </c>
       <c r="C41" s="7">
-        <v>12.4</v>
+        <v>9.9700000000000006</v>
       </c>
       <c r="D41" s="7">
         <v>12.62</v>
       </c>
       <c r="E41" s="7">
-        <v>9.61</v>
+        <v>9.7100000000000009</v>
       </c>
       <c r="F41" s="10">
-        <v>2.2999999999999998</v>
+        <v>-2.4300000000000002</v>
       </c>
       <c r="G41" s="10">
-        <v>22.77</v>
+        <v>-19.600000000000001</v>
       </c>
       <c r="H41" s="9">
         <v>0</v>
@@ -3346,25 +3353,25 @@
     </row>
     <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
-        <v>43617</v>
+        <v>43647</v>
       </c>
       <c r="B42" s="7">
-        <v>11.9</v>
+        <v>10.1</v>
       </c>
       <c r="C42" s="7">
-        <v>10.1</v>
+        <v>12.4</v>
       </c>
       <c r="D42" s="7">
-        <v>11.84</v>
+        <v>12.62</v>
       </c>
       <c r="E42" s="7">
-        <v>8.2100000000000009</v>
+        <v>9.61</v>
       </c>
       <c r="F42" s="8">
-        <v>-1.8</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="G42" s="8">
-        <v>-15.13</v>
+        <v>22.77</v>
       </c>
       <c r="H42" s="9">
         <v>0</v>
@@ -3399,31 +3406,31 @@
     </row>
     <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
-        <v>43586</v>
+        <v>43617</v>
       </c>
       <c r="B43" s="7">
-        <v>12.81</v>
+        <v>11.9</v>
       </c>
       <c r="C43" s="7">
-        <v>11.9</v>
+        <v>10.1</v>
       </c>
       <c r="D43" s="7">
-        <v>13.35</v>
+        <v>11.84</v>
       </c>
       <c r="E43" s="7">
-        <v>11.31</v>
-      </c>
-      <c r="F43" s="8">
-        <v>-0.91</v>
-      </c>
-      <c r="G43" s="8">
-        <v>-7.1</v>
+        <v>8.2100000000000009</v>
+      </c>
+      <c r="F43" s="10">
+        <v>-1.8</v>
+      </c>
+      <c r="G43" s="10">
+        <v>-15.13</v>
       </c>
       <c r="H43" s="9">
         <v>0</v>
       </c>
-      <c r="I43" s="8">
-        <v>-100</v>
+      <c r="I43" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J43" s="9" t="s">
         <v>17</v>
@@ -3437,8 +3444,8 @@
       <c r="M43" s="9">
         <v>0</v>
       </c>
-      <c r="N43" s="8">
-        <v>-100</v>
+      <c r="N43" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O43" s="9" t="s">
         <v>17</v>
@@ -3452,31 +3459,31 @@
     </row>
     <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
-        <v>43556</v>
+        <v>43586</v>
       </c>
       <c r="B44" s="7">
-        <v>13.8</v>
+        <v>12.81</v>
       </c>
       <c r="C44" s="7">
-        <v>12.81</v>
+        <v>11.9</v>
       </c>
       <c r="D44" s="7">
-        <v>15.45</v>
+        <v>13.35</v>
       </c>
       <c r="E44" s="7">
-        <v>11.91</v>
-      </c>
-      <c r="F44" s="8">
-        <v>-0.99</v>
-      </c>
-      <c r="G44" s="8">
-        <v>-7.17</v>
+        <v>11.31</v>
+      </c>
+      <c r="F44" s="10">
+        <v>-0.91</v>
+      </c>
+      <c r="G44" s="10">
+        <v>-7.1</v>
       </c>
       <c r="H44" s="9">
-        <v>0.61699999999999999</v>
-      </c>
-      <c r="I44" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="I44" s="10">
+        <v>-100</v>
       </c>
       <c r="J44" s="9" t="s">
         <v>17</v>
@@ -3488,10 +3495,10 @@
         <v>17</v>
       </c>
       <c r="M44" s="9">
-        <v>0.61699999999999999</v>
-      </c>
-      <c r="N44" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="N44" s="10">
+        <v>-100</v>
       </c>
       <c r="O44" s="9" t="s">
         <v>17</v>
@@ -3505,28 +3512,28 @@
     </row>
     <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
-        <v>43525</v>
+        <v>43556</v>
       </c>
       <c r="B45" s="7">
-        <v>9.8000000000000007</v>
+        <v>13.8</v>
       </c>
       <c r="C45" s="7">
-        <v>13.8</v>
+        <v>12.81</v>
       </c>
       <c r="D45" s="7">
-        <v>16.73</v>
+        <v>15.45</v>
       </c>
       <c r="E45" s="7">
-        <v>10.210000000000001</v>
+        <v>11.91</v>
       </c>
       <c r="F45" s="10">
-        <v>4</v>
+        <v>-0.99</v>
       </c>
       <c r="G45" s="10">
-        <v>40.82</v>
+        <v>-7.17</v>
       </c>
       <c r="H45" s="9">
-        <v>0</v>
+        <v>0.61699999999999999</v>
       </c>
       <c r="I45" s="9" t="s">
         <v>17</v>
@@ -3535,13 +3542,13 @@
         <v>17</v>
       </c>
       <c r="K45" s="9">
-        <v>0</v>
+        <v>0.61699999999999999</v>
       </c>
       <c r="L45" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M45" s="9">
-        <v>0</v>
+        <v>0.61699999999999999</v>
       </c>
       <c r="N45" s="9" t="s">
         <v>17</v>
@@ -3550,7 +3557,7 @@
         <v>17</v>
       </c>
       <c r="P45" s="9">
-        <v>0</v>
+        <v>0.61699999999999999</v>
       </c>
       <c r="Q45" s="9" t="s">
         <v>17</v>
@@ -3558,25 +3565,25 @@
     </row>
     <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
-        <v>43497</v>
+        <v>43525</v>
       </c>
       <c r="B46" s="7">
-        <v>6.9</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="C46" s="7">
-        <v>9.8000000000000007</v>
+        <v>13.8</v>
       </c>
       <c r="D46" s="7">
-        <v>10.99</v>
+        <v>16.73</v>
       </c>
       <c r="E46" s="7">
-        <v>6.6</v>
-      </c>
-      <c r="F46" s="10">
-        <v>2.9</v>
-      </c>
-      <c r="G46" s="10">
-        <v>42.03</v>
+        <v>10.210000000000001</v>
+      </c>
+      <c r="F46" s="8">
+        <v>4</v>
+      </c>
+      <c r="G46" s="8">
+        <v>40.82</v>
       </c>
       <c r="H46" s="9">
         <v>0</v>
@@ -3611,25 +3618,25 @@
     </row>
     <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
-        <v>43466</v>
+        <v>43497</v>
       </c>
       <c r="B47" s="7">
-        <v>6.73</v>
+        <v>6.9</v>
       </c>
       <c r="C47" s="7">
-        <v>6.9</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="D47" s="7">
-        <v>7.14</v>
+        <v>10.99</v>
       </c>
       <c r="E47" s="7">
-        <v>5.96</v>
-      </c>
-      <c r="F47" s="10">
-        <v>0.17</v>
-      </c>
-      <c r="G47" s="10">
-        <v>2.5299999999999998</v>
+        <v>6.6</v>
+      </c>
+      <c r="F47" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="G47" s="8">
+        <v>42.03</v>
       </c>
       <c r="H47" s="9">
         <v>0</v>
@@ -3664,25 +3671,25 @@
     </row>
     <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
-        <v>43435</v>
+        <v>43466</v>
       </c>
       <c r="B48" s="7">
-        <v>7</v>
+        <v>6.73</v>
       </c>
       <c r="C48" s="7">
-        <v>6.73</v>
+        <v>6.9</v>
       </c>
       <c r="D48" s="7">
-        <v>7.04</v>
+        <v>7.14</v>
       </c>
       <c r="E48" s="7">
-        <v>6.5</v>
+        <v>5.96</v>
       </c>
       <c r="F48" s="8">
-        <v>-0.27</v>
+        <v>0.17</v>
       </c>
       <c r="G48" s="8">
-        <v>-3.86</v>
+        <v>2.5299999999999998</v>
       </c>
       <c r="H48" s="9">
         <v>0</v>
@@ -3717,25 +3724,25 @@
     </row>
     <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
-        <v>43405</v>
+        <v>43435</v>
       </c>
       <c r="B49" s="7">
         <v>7</v>
       </c>
       <c r="C49" s="7">
-        <v>7</v>
+        <v>6.73</v>
       </c>
       <c r="D49" s="7">
-        <v>7.3</v>
+        <v>7.04</v>
       </c>
       <c r="E49" s="7">
-        <v>6.66</v>
-      </c>
-      <c r="F49" s="9">
-        <v>0</v>
-      </c>
-      <c r="G49" s="9">
-        <v>0</v>
+        <v>6.5</v>
+      </c>
+      <c r="F49" s="10">
+        <v>-0.27</v>
+      </c>
+      <c r="G49" s="10">
+        <v>-3.86</v>
       </c>
       <c r="H49" s="9">
         <v>0</v>
@@ -3770,25 +3777,25 @@
     </row>
     <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
-        <v>43374</v>
+        <v>43405</v>
       </c>
       <c r="B50" s="7">
-        <v>7.25</v>
+        <v>7</v>
       </c>
       <c r="C50" s="7">
         <v>7</v>
       </c>
       <c r="D50" s="7">
-        <v>9.1</v>
+        <v>7.3</v>
       </c>
       <c r="E50" s="7">
-        <v>6.46</v>
-      </c>
-      <c r="F50" s="8">
-        <v>-0.25</v>
-      </c>
-      <c r="G50" s="8">
-        <v>-3.45</v>
+        <v>6.66</v>
+      </c>
+      <c r="F50" s="9">
+        <v>0</v>
+      </c>
+      <c r="G50" s="9">
+        <v>0</v>
       </c>
       <c r="H50" s="9">
         <v>0</v>
@@ -3823,25 +3830,25 @@
     </row>
     <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
-        <v>43344</v>
+        <v>43374</v>
       </c>
       <c r="B51" s="7">
-        <v>8.6999999999999993</v>
+        <v>7.25</v>
       </c>
       <c r="C51" s="7">
-        <v>7.25</v>
+        <v>7</v>
       </c>
       <c r="D51" s="7">
-        <v>8.7200000000000006</v>
+        <v>9.1</v>
       </c>
       <c r="E51" s="7">
-        <v>6.41</v>
-      </c>
-      <c r="F51" s="8">
-        <v>-1.45</v>
-      </c>
-      <c r="G51" s="8">
-        <v>-16.670000000000002</v>
+        <v>6.46</v>
+      </c>
+      <c r="F51" s="10">
+        <v>-0.25</v>
+      </c>
+      <c r="G51" s="10">
+        <v>-3.45</v>
       </c>
       <c r="H51" s="9">
         <v>0</v>
@@ -3876,25 +3883,25 @@
     </row>
     <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
-        <v>43313</v>
+        <v>43344</v>
       </c>
       <c r="B52" s="7">
-        <v>7.46</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="C52" s="7">
-        <v>8.6999999999999993</v>
+        <v>7.25</v>
       </c>
       <c r="D52" s="7">
-        <v>8.77</v>
+        <v>8.7200000000000006</v>
       </c>
       <c r="E52" s="7">
-        <v>6.3</v>
+        <v>6.41</v>
       </c>
       <c r="F52" s="10">
-        <v>1.24</v>
+        <v>-1.45</v>
       </c>
       <c r="G52" s="10">
-        <v>16.62</v>
+        <v>-16.670000000000002</v>
       </c>
       <c r="H52" s="9">
         <v>0</v>
@@ -3929,25 +3936,25 @@
     </row>
     <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
-        <v>43282</v>
+        <v>43313</v>
       </c>
       <c r="B53" s="7">
-        <v>9.35</v>
+        <v>7.46</v>
       </c>
       <c r="C53" s="7">
-        <v>7.46</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="D53" s="7">
-        <v>9.35</v>
+        <v>8.77</v>
       </c>
       <c r="E53" s="7">
-        <v>6.71</v>
+        <v>6.3</v>
       </c>
       <c r="F53" s="8">
-        <v>-1.89</v>
+        <v>1.24</v>
       </c>
       <c r="G53" s="8">
-        <v>-20.21</v>
+        <v>16.62</v>
       </c>
       <c r="H53" s="9">
         <v>0</v>
@@ -3982,25 +3989,25 @@
     </row>
     <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
-        <v>43252</v>
+        <v>43282</v>
       </c>
       <c r="B54" s="7">
-        <v>7.24</v>
+        <v>9.35</v>
       </c>
       <c r="C54" s="7">
+        <v>7.46</v>
+      </c>
+      <c r="D54" s="7">
         <v>9.35</v>
       </c>
-      <c r="D54" s="7">
-        <v>12.04</v>
-      </c>
       <c r="E54" s="7">
-        <v>7</v>
+        <v>6.71</v>
       </c>
       <c r="F54" s="10">
-        <v>2.11</v>
+        <v>-1.89</v>
       </c>
       <c r="G54" s="10">
-        <v>29.14</v>
+        <v>-20.21</v>
       </c>
       <c r="H54" s="9">
         <v>0</v>
@@ -4035,25 +4042,25 @@
     </row>
     <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
-        <v>43221</v>
+        <v>43252</v>
       </c>
       <c r="B55" s="7">
-        <v>9.3000000000000007</v>
+        <v>7.24</v>
       </c>
       <c r="C55" s="7">
-        <v>7.24</v>
+        <v>9.35</v>
       </c>
       <c r="D55" s="7">
-        <v>9.89</v>
+        <v>12.04</v>
       </c>
       <c r="E55" s="7">
         <v>7</v>
       </c>
       <c r="F55" s="8">
-        <v>-2.06</v>
+        <v>2.11</v>
       </c>
       <c r="G55" s="8">
-        <v>-22.15</v>
+        <v>29.14</v>
       </c>
       <c r="H55" s="9">
         <v>0</v>
@@ -4088,25 +4095,25 @@
     </row>
     <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
-        <v>43191</v>
+        <v>43221</v>
       </c>
       <c r="B56" s="7">
-        <v>9.9</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="C56" s="7">
-        <v>9.3000000000000007</v>
+        <v>7.24</v>
       </c>
       <c r="D56" s="7">
-        <v>10.41</v>
+        <v>9.89</v>
       </c>
       <c r="E56" s="7">
-        <v>8.91</v>
-      </c>
-      <c r="F56" s="8">
-        <v>-0.6</v>
-      </c>
-      <c r="G56" s="8">
-        <v>-6.06</v>
+        <v>7</v>
+      </c>
+      <c r="F56" s="10">
+        <v>-2.06</v>
+      </c>
+      <c r="G56" s="10">
+        <v>-22.15</v>
       </c>
       <c r="H56" s="9">
         <v>0</v>
@@ -4141,25 +4148,25 @@
     </row>
     <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
-        <v>43160</v>
+        <v>43191</v>
       </c>
       <c r="B57" s="7">
-        <v>10.82</v>
+        <v>9.9</v>
       </c>
       <c r="C57" s="7">
-        <v>9.9</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="D57" s="7">
-        <v>11.14</v>
+        <v>10.41</v>
       </c>
       <c r="E57" s="7">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="F57" s="8">
-        <v>-0.92</v>
-      </c>
-      <c r="G57" s="8">
-        <v>-8.5</v>
+        <v>8.91</v>
+      </c>
+      <c r="F57" s="10">
+        <v>-0.6</v>
+      </c>
+      <c r="G57" s="10">
+        <v>-6.06</v>
       </c>
       <c r="H57" s="9">
         <v>0</v>
@@ -4194,25 +4201,25 @@
     </row>
     <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
-        <v>43132</v>
+        <v>43160</v>
       </c>
       <c r="B58" s="7">
-        <v>10.99</v>
+        <v>10.82</v>
       </c>
       <c r="C58" s="7">
-        <v>10.82</v>
+        <v>9.9</v>
       </c>
       <c r="D58" s="7">
-        <v>11.46</v>
+        <v>11.14</v>
       </c>
       <c r="E58" s="7">
-        <v>9.9600000000000009</v>
-      </c>
-      <c r="F58" s="8">
-        <v>-0.17</v>
-      </c>
-      <c r="G58" s="8">
-        <v>-1.55</v>
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="F58" s="10">
+        <v>-0.92</v>
+      </c>
+      <c r="G58" s="10">
+        <v>-8.5</v>
       </c>
       <c r="H58" s="9">
         <v>0</v>
@@ -4247,25 +4254,25 @@
     </row>
     <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
-        <v>43101</v>
+        <v>43132</v>
       </c>
       <c r="B59" s="7">
-        <v>11.5</v>
+        <v>10.99</v>
       </c>
       <c r="C59" s="7">
-        <v>10.99</v>
+        <v>10.82</v>
       </c>
       <c r="D59" s="7">
-        <v>12.3</v>
+        <v>11.46</v>
       </c>
       <c r="E59" s="7">
-        <v>10.46</v>
-      </c>
-      <c r="F59" s="8">
-        <v>-0.51</v>
-      </c>
-      <c r="G59" s="8">
-        <v>-4.43</v>
+        <v>9.9600000000000009</v>
+      </c>
+      <c r="F59" s="10">
+        <v>-0.17</v>
+      </c>
+      <c r="G59" s="10">
+        <v>-1.55</v>
       </c>
       <c r="H59" s="9">
         <v>0</v>
@@ -4300,25 +4307,25 @@
     </row>
     <row r="60" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
-        <v>43070</v>
+        <v>43101</v>
       </c>
       <c r="B60" s="7">
-        <v>13.89</v>
+        <v>11.5</v>
       </c>
       <c r="C60" s="7">
-        <v>11.5</v>
+        <v>10.99</v>
       </c>
       <c r="D60" s="7">
-        <v>14.09</v>
+        <v>12.3</v>
       </c>
       <c r="E60" s="7">
-        <v>10.75</v>
-      </c>
-      <c r="F60" s="8">
-        <v>-2.39</v>
-      </c>
-      <c r="G60" s="8">
-        <v>-17.21</v>
+        <v>10.46</v>
+      </c>
+      <c r="F60" s="10">
+        <v>-0.51</v>
+      </c>
+      <c r="G60" s="10">
+        <v>-4.43</v>
       </c>
       <c r="H60" s="9">
         <v>0</v>
@@ -4353,25 +4360,25 @@
     </row>
     <row r="61" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
-        <v>43040</v>
+        <v>43070</v>
       </c>
       <c r="B61" s="7">
-        <v>10.63</v>
+        <v>13.89</v>
       </c>
       <c r="C61" s="7">
-        <v>13.89</v>
+        <v>11.5</v>
       </c>
       <c r="D61" s="7">
-        <v>19.600000000000001</v>
+        <v>14.09</v>
       </c>
       <c r="E61" s="7">
-        <v>11.1</v>
+        <v>10.75</v>
       </c>
       <c r="F61" s="10">
-        <v>3.26</v>
+        <v>-2.39</v>
       </c>
       <c r="G61" s="10">
-        <v>30.67</v>
+        <v>-17.21</v>
       </c>
       <c r="H61" s="9">
         <v>0</v>
@@ -4406,25 +4413,25 @@
     </row>
     <row r="62" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
-        <v>43009</v>
+        <v>43040</v>
       </c>
       <c r="B62" s="7">
-        <v>14.87</v>
+        <v>10.63</v>
       </c>
       <c r="C62" s="7">
-        <v>10.63</v>
+        <v>13.89</v>
       </c>
       <c r="D62" s="7">
-        <v>15.67</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="E62" s="7">
-        <v>9.9600000000000009</v>
+        <v>11.1</v>
       </c>
       <c r="F62" s="8">
-        <v>-4.24</v>
+        <v>3.26</v>
       </c>
       <c r="G62" s="8">
-        <v>-28.51</v>
+        <v>30.67</v>
       </c>
       <c r="H62" s="9">
         <v>0</v>
@@ -4459,25 +4466,25 @@
     </row>
     <row r="63" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
-        <v>42979</v>
+        <v>43009</v>
       </c>
       <c r="B63" s="7">
-        <v>16.45</v>
+        <v>14.87</v>
       </c>
       <c r="C63" s="7">
-        <v>14.87</v>
+        <v>10.63</v>
       </c>
       <c r="D63" s="7">
-        <v>18.5</v>
+        <v>15.67</v>
       </c>
       <c r="E63" s="7">
-        <v>14.55</v>
-      </c>
-      <c r="F63" s="8">
-        <v>-1.58</v>
-      </c>
-      <c r="G63" s="8">
-        <v>-9.6</v>
+        <v>9.9600000000000009</v>
+      </c>
+      <c r="F63" s="10">
+        <v>-4.24</v>
+      </c>
+      <c r="G63" s="10">
+        <v>-28.51</v>
       </c>
       <c r="H63" s="9">
         <v>0</v>
@@ -4512,25 +4519,25 @@
     </row>
     <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
-        <v>42948</v>
+        <v>42979</v>
       </c>
       <c r="B64" s="7">
-        <v>17.21</v>
+        <v>16.45</v>
       </c>
       <c r="C64" s="7">
-        <v>16.45</v>
+        <v>14.87</v>
       </c>
       <c r="D64" s="7">
-        <v>18.05</v>
+        <v>18.5</v>
       </c>
       <c r="E64" s="7">
-        <v>16.309999999999999</v>
-      </c>
-      <c r="F64" s="8">
-        <v>-0.76</v>
-      </c>
-      <c r="G64" s="8">
-        <v>-4.42</v>
+        <v>14.55</v>
+      </c>
+      <c r="F64" s="10">
+        <v>-1.58</v>
+      </c>
+      <c r="G64" s="10">
+        <v>-9.6</v>
       </c>
       <c r="H64" s="9">
         <v>0</v>
@@ -4565,25 +4572,25 @@
     </row>
     <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
-        <v>42917</v>
+        <v>42948</v>
       </c>
       <c r="B65" s="7">
-        <v>18.600000000000001</v>
+        <v>17.21</v>
       </c>
       <c r="C65" s="7">
-        <v>17.21</v>
+        <v>16.45</v>
       </c>
       <c r="D65" s="7">
-        <v>20.07</v>
+        <v>18.05</v>
       </c>
       <c r="E65" s="7">
-        <v>17</v>
-      </c>
-      <c r="F65" s="8">
-        <v>-1.39</v>
-      </c>
-      <c r="G65" s="8">
-        <v>-7.47</v>
+        <v>16.309999999999999</v>
+      </c>
+      <c r="F65" s="10">
+        <v>-0.76</v>
+      </c>
+      <c r="G65" s="10">
+        <v>-4.42</v>
       </c>
       <c r="H65" s="9">
         <v>0</v>
@@ -4618,25 +4625,25 @@
     </row>
     <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
-        <v>42887</v>
+        <v>42917</v>
       </c>
       <c r="B66" s="7">
-        <v>17.8</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="C66" s="7">
-        <v>18.600000000000001</v>
+        <v>17.21</v>
       </c>
       <c r="D66" s="7">
-        <v>20.100000000000001</v>
+        <v>20.07</v>
       </c>
       <c r="E66" s="7">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="F66" s="10">
-        <v>0.8</v>
+        <v>-1.39</v>
       </c>
       <c r="G66" s="10">
-        <v>4.49</v>
+        <v>-7.47</v>
       </c>
       <c r="H66" s="9">
         <v>0</v>
@@ -4671,25 +4678,25 @@
     </row>
     <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
-        <v>42856</v>
+        <v>42887</v>
       </c>
       <c r="B67" s="7">
-        <v>15.1</v>
+        <v>17.8</v>
       </c>
       <c r="C67" s="7">
-        <v>17.8</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="D67" s="7">
-        <v>20.25</v>
+        <v>20.100000000000001</v>
       </c>
       <c r="E67" s="7">
-        <v>14.71</v>
-      </c>
-      <c r="F67" s="10">
-        <v>2.7</v>
-      </c>
-      <c r="G67" s="10">
-        <v>17.88</v>
+        <v>17.2</v>
+      </c>
+      <c r="F67" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="G67" s="8">
+        <v>4.49</v>
       </c>
       <c r="H67" s="9">
         <v>0</v>
@@ -4724,25 +4731,25 @@
     </row>
     <row r="68" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
-        <v>42826</v>
+        <v>42856</v>
       </c>
       <c r="B68" s="7">
-        <v>13.25</v>
+        <v>15.1</v>
       </c>
       <c r="C68" s="7">
-        <v>15.1</v>
+        <v>17.8</v>
       </c>
       <c r="D68" s="7">
-        <v>18.3</v>
+        <v>20.25</v>
       </c>
       <c r="E68" s="7">
-        <v>9.6300000000000008</v>
-      </c>
-      <c r="F68" s="10">
-        <v>1.85</v>
-      </c>
-      <c r="G68" s="10">
-        <v>13.96</v>
+        <v>14.71</v>
+      </c>
+      <c r="F68" s="8">
+        <v>2.7</v>
+      </c>
+      <c r="G68" s="8">
+        <v>17.88</v>
       </c>
       <c r="H68" s="9">
         <v>0</v>
@@ -4777,25 +4784,25 @@
     </row>
     <row r="69" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
-        <v>42795</v>
+        <v>42826</v>
       </c>
       <c r="B69" s="7">
-        <v>15.14</v>
+        <v>13.25</v>
       </c>
       <c r="C69" s="7">
-        <v>13.25</v>
+        <v>15.1</v>
       </c>
       <c r="D69" s="7">
-        <v>16.260000000000002</v>
+        <v>18.3</v>
       </c>
       <c r="E69" s="7">
-        <v>13</v>
+        <v>9.6300000000000008</v>
       </c>
       <c r="F69" s="8">
-        <v>-1.89</v>
+        <v>1.85</v>
       </c>
       <c r="G69" s="8">
-        <v>-12.48</v>
+        <v>13.96</v>
       </c>
       <c r="H69" s="9">
         <v>0</v>
@@ -4830,25 +4837,25 @@
     </row>
     <row r="70" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
-        <v>42767</v>
+        <v>42795</v>
       </c>
       <c r="B70" s="7">
-        <v>17.66</v>
+        <v>15.14</v>
       </c>
       <c r="C70" s="7">
-        <v>15.14</v>
+        <v>13.25</v>
       </c>
       <c r="D70" s="7">
-        <v>19.04</v>
+        <v>16.260000000000002</v>
       </c>
       <c r="E70" s="7">
-        <v>14.8</v>
-      </c>
-      <c r="F70" s="8">
-        <v>-2.52</v>
-      </c>
-      <c r="G70" s="8">
-        <v>-14.27</v>
+        <v>13</v>
+      </c>
+      <c r="F70" s="10">
+        <v>-1.89</v>
+      </c>
+      <c r="G70" s="10">
+        <v>-12.48</v>
       </c>
       <c r="H70" s="9">
         <v>0</v>
@@ -4883,25 +4890,25 @@
     </row>
     <row r="71" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
-        <v>42736</v>
+        <v>42767</v>
       </c>
       <c r="B71" s="7">
-        <v>21.3</v>
+        <v>17.66</v>
       </c>
       <c r="C71" s="7">
-        <v>17.66</v>
+        <v>15.14</v>
       </c>
       <c r="D71" s="7">
-        <v>22.13</v>
+        <v>19.04</v>
       </c>
       <c r="E71" s="7">
-        <v>16.16</v>
-      </c>
-      <c r="F71" s="8">
-        <v>-3.64</v>
-      </c>
-      <c r="G71" s="8">
-        <v>-17.09</v>
+        <v>14.8</v>
+      </c>
+      <c r="F71" s="10">
+        <v>-2.52</v>
+      </c>
+      <c r="G71" s="10">
+        <v>-14.27</v>
       </c>
       <c r="H71" s="9">
         <v>0</v>
@@ -4936,25 +4943,25 @@
     </row>
     <row r="72" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
-        <v>42705</v>
+        <v>42736</v>
       </c>
       <c r="B72" s="7">
-        <v>22.79</v>
+        <v>21.3</v>
       </c>
       <c r="C72" s="7">
-        <v>21.3</v>
+        <v>17.66</v>
       </c>
       <c r="D72" s="7">
-        <v>25.79</v>
+        <v>22.13</v>
       </c>
       <c r="E72" s="7">
-        <v>20.6</v>
-      </c>
-      <c r="F72" s="8">
-        <v>-1.49</v>
-      </c>
-      <c r="G72" s="8">
-        <v>-6.54</v>
+        <v>16.16</v>
+      </c>
+      <c r="F72" s="10">
+        <v>-3.64</v>
+      </c>
+      <c r="G72" s="10">
+        <v>-17.09</v>
       </c>
       <c r="H72" s="9">
         <v>0</v>
@@ -4989,25 +4996,25 @@
     </row>
     <row r="73" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
-        <v>42675</v>
+        <v>42705</v>
       </c>
       <c r="B73" s="7">
-        <v>21.24</v>
+        <v>22.79</v>
       </c>
       <c r="C73" s="7">
-        <v>22.79</v>
+        <v>21.3</v>
       </c>
       <c r="D73" s="7">
-        <v>24.5</v>
+        <v>25.79</v>
       </c>
       <c r="E73" s="7">
-        <v>19</v>
+        <v>20.6</v>
       </c>
       <c r="F73" s="10">
-        <v>1.55</v>
+        <v>-1.49</v>
       </c>
       <c r="G73" s="10">
-        <v>7.3</v>
+        <v>-6.54</v>
       </c>
       <c r="H73" s="9">
         <v>0</v>
@@ -5042,25 +5049,25 @@
     </row>
     <row r="74" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
-        <v>42644</v>
+        <v>42675</v>
       </c>
       <c r="B74" s="7">
-        <v>25.91</v>
+        <v>21.24</v>
       </c>
       <c r="C74" s="7">
-        <v>21.24</v>
+        <v>22.79</v>
       </c>
       <c r="D74" s="7">
-        <v>26.5</v>
+        <v>24.5</v>
       </c>
       <c r="E74" s="7">
-        <v>21.04</v>
+        <v>19</v>
       </c>
       <c r="F74" s="8">
-        <v>-4.67</v>
+        <v>1.55</v>
       </c>
       <c r="G74" s="8">
-        <v>-18.02</v>
+        <v>7.3</v>
       </c>
       <c r="H74" s="9">
         <v>0</v>
@@ -5095,25 +5102,25 @@
     </row>
     <row r="75" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
-        <v>42614</v>
+        <v>42644</v>
       </c>
       <c r="B75" s="7">
-        <v>28.4</v>
+        <v>25.91</v>
       </c>
       <c r="C75" s="7">
-        <v>25.91</v>
+        <v>21.24</v>
       </c>
       <c r="D75" s="7">
-        <v>29</v>
+        <v>26.5</v>
       </c>
       <c r="E75" s="7">
-        <v>25.91</v>
-      </c>
-      <c r="F75" s="8">
-        <v>-2.4900000000000002</v>
-      </c>
-      <c r="G75" s="8">
-        <v>-8.77</v>
+        <v>21.04</v>
+      </c>
+      <c r="F75" s="10">
+        <v>-4.67</v>
+      </c>
+      <c r="G75" s="10">
+        <v>-18.02</v>
       </c>
       <c r="H75" s="9">
         <v>0</v>
@@ -5148,25 +5155,25 @@
     </row>
     <row r="76" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
-        <v>42583</v>
+        <v>42614</v>
       </c>
       <c r="B76" s="7">
-        <v>28.82</v>
+        <v>28.4</v>
       </c>
       <c r="C76" s="7">
-        <v>28.4</v>
+        <v>25.91</v>
       </c>
       <c r="D76" s="7">
-        <v>29.19</v>
+        <v>29</v>
       </c>
       <c r="E76" s="7">
-        <v>25.99</v>
-      </c>
-      <c r="F76" s="8">
-        <v>-0.42</v>
-      </c>
-      <c r="G76" s="8">
-        <v>-1.46</v>
+        <v>25.91</v>
+      </c>
+      <c r="F76" s="10">
+        <v>-2.4900000000000002</v>
+      </c>
+      <c r="G76" s="10">
+        <v>-8.77</v>
       </c>
       <c r="H76" s="9">
         <v>0</v>
@@ -5201,25 +5208,25 @@
     </row>
     <row r="77" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
-        <v>42552</v>
+        <v>42583</v>
       </c>
       <c r="B77" s="7">
-        <v>32</v>
+        <v>28.82</v>
       </c>
       <c r="C77" s="7">
-        <v>28.82</v>
+        <v>28.4</v>
       </c>
       <c r="D77" s="7">
-        <v>33.19</v>
+        <v>29.19</v>
       </c>
       <c r="E77" s="7">
-        <v>28.82</v>
-      </c>
-      <c r="F77" s="8">
-        <v>-3.18</v>
-      </c>
-      <c r="G77" s="8">
-        <v>-9.94</v>
+        <v>25.99</v>
+      </c>
+      <c r="F77" s="10">
+        <v>-0.42</v>
+      </c>
+      <c r="G77" s="10">
+        <v>-1.46</v>
       </c>
       <c r="H77" s="9">
         <v>0</v>
@@ -5254,25 +5261,25 @@
     </row>
     <row r="78" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
-        <v>42522</v>
+        <v>42552</v>
       </c>
       <c r="B78" s="7">
-        <v>34.03</v>
+        <v>32</v>
       </c>
       <c r="C78" s="7">
-        <v>32</v>
+        <v>28.82</v>
       </c>
       <c r="D78" s="7">
-        <v>35</v>
+        <v>33.19</v>
       </c>
       <c r="E78" s="7">
-        <v>31.89</v>
-      </c>
-      <c r="F78" s="8">
-        <v>-2.0299999999999998</v>
-      </c>
-      <c r="G78" s="8">
-        <v>-5.97</v>
+        <v>28.82</v>
+      </c>
+      <c r="F78" s="10">
+        <v>-3.18</v>
+      </c>
+      <c r="G78" s="10">
+        <v>-9.94</v>
       </c>
       <c r="H78" s="9">
         <v>0</v>
@@ -5307,25 +5314,25 @@
     </row>
     <row r="79" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
-        <v>42491</v>
+        <v>42522</v>
       </c>
       <c r="B79" s="7">
-        <v>38.5</v>
+        <v>34.03</v>
       </c>
       <c r="C79" s="7">
-        <v>34.03</v>
+        <v>32</v>
       </c>
       <c r="D79" s="7">
-        <v>37.24</v>
+        <v>35</v>
       </c>
       <c r="E79" s="7">
-        <v>30.31</v>
-      </c>
-      <c r="F79" s="8">
-        <v>-4.47</v>
-      </c>
-      <c r="G79" s="8">
-        <v>-11.61</v>
+        <v>31.89</v>
+      </c>
+      <c r="F79" s="10">
+        <v>-2.0299999999999998</v>
+      </c>
+      <c r="G79" s="10">
+        <v>-5.97</v>
       </c>
       <c r="H79" s="9">
         <v>0</v>
@@ -5360,25 +5367,25 @@
     </row>
     <row r="80" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
-        <v>42461</v>
+        <v>42491</v>
       </c>
       <c r="B80" s="7">
-        <v>40.01</v>
+        <v>38.5</v>
       </c>
       <c r="C80" s="7">
-        <v>38.5</v>
+        <v>34.03</v>
       </c>
       <c r="D80" s="7">
-        <v>44.21</v>
+        <v>37.24</v>
       </c>
       <c r="E80" s="7">
-        <v>36.799999999999997</v>
-      </c>
-      <c r="F80" s="8">
-        <v>-1.51</v>
-      </c>
-      <c r="G80" s="8">
-        <v>-3.77</v>
+        <v>30.31</v>
+      </c>
+      <c r="F80" s="10">
+        <v>-4.47</v>
+      </c>
+      <c r="G80" s="10">
+        <v>-11.61</v>
       </c>
       <c r="H80" s="9">
         <v>0</v>
@@ -5413,25 +5420,25 @@
     </row>
     <row r="81" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
-        <v>42430</v>
+        <v>42461</v>
       </c>
       <c r="B81" s="7">
-        <v>40.39</v>
+        <v>40.01</v>
       </c>
       <c r="C81" s="7">
-        <v>40.01</v>
+        <v>38.5</v>
       </c>
       <c r="D81" s="7">
-        <v>42.1</v>
+        <v>44.21</v>
       </c>
       <c r="E81" s="7">
-        <v>36</v>
-      </c>
-      <c r="F81" s="8">
-        <v>-0.38</v>
-      </c>
-      <c r="G81" s="8">
-        <v>-0.94</v>
+        <v>36.799999999999997</v>
+      </c>
+      <c r="F81" s="10">
+        <v>-1.51</v>
+      </c>
+      <c r="G81" s="10">
+        <v>-3.77</v>
       </c>
       <c r="H81" s="9">
         <v>0</v>
@@ -5466,25 +5473,25 @@
     </row>
     <row r="82" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
-        <v>42401</v>
+        <v>42430</v>
       </c>
       <c r="B82" s="7">
-        <v>48.5</v>
+        <v>40.39</v>
       </c>
       <c r="C82" s="7">
-        <v>40.39</v>
+        <v>40.01</v>
       </c>
       <c r="D82" s="7">
-        <v>47.51</v>
+        <v>42.1</v>
       </c>
       <c r="E82" s="7">
-        <v>38.86</v>
-      </c>
-      <c r="F82" s="8">
-        <v>-8.11</v>
-      </c>
-      <c r="G82" s="8">
-        <v>-16.72</v>
+        <v>36</v>
+      </c>
+      <c r="F82" s="10">
+        <v>-0.38</v>
+      </c>
+      <c r="G82" s="10">
+        <v>-0.94</v>
       </c>
       <c r="H82" s="9">
         <v>0</v>
@@ -5519,25 +5526,25 @@
     </row>
     <row r="83" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
-        <v>42370</v>
+        <v>42401</v>
       </c>
       <c r="B83" s="7">
-        <v>50.76</v>
+        <v>48.5</v>
       </c>
       <c r="C83" s="7">
-        <v>48.5</v>
+        <v>40.39</v>
       </c>
       <c r="D83" s="7">
-        <v>58.2</v>
+        <v>47.51</v>
       </c>
       <c r="E83" s="7">
-        <v>44.55</v>
-      </c>
-      <c r="F83" s="8">
-        <v>-2.2599999999999998</v>
-      </c>
-      <c r="G83" s="8">
-        <v>-4.45</v>
+        <v>38.86</v>
+      </c>
+      <c r="F83" s="10">
+        <v>-8.11</v>
+      </c>
+      <c r="G83" s="10">
+        <v>-16.72</v>
       </c>
       <c r="H83" s="9">
         <v>0</v>
@@ -5572,25 +5579,25 @@
     </row>
     <row r="84" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
-        <v>42339</v>
+        <v>42370</v>
       </c>
       <c r="B84" s="7">
-        <v>52.07</v>
+        <v>50.76</v>
       </c>
       <c r="C84" s="7">
-        <v>50.76</v>
+        <v>48.5</v>
       </c>
       <c r="D84" s="7">
-        <v>60.2</v>
+        <v>58.2</v>
       </c>
       <c r="E84" s="7">
-        <v>50.01</v>
-      </c>
-      <c r="F84" s="8">
-        <v>-1.31</v>
-      </c>
-      <c r="G84" s="8">
-        <v>-2.52</v>
+        <v>44.55</v>
+      </c>
+      <c r="F84" s="10">
+        <v>-2.2599999999999998</v>
+      </c>
+      <c r="G84" s="10">
+        <v>-4.45</v>
       </c>
       <c r="H84" s="9">
         <v>0</v>
@@ -5625,25 +5632,25 @@
     </row>
     <row r="85" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
-        <v>42309</v>
+        <v>42339</v>
       </c>
       <c r="B85" s="7">
-        <v>55.5</v>
+        <v>52.07</v>
       </c>
       <c r="C85" s="7">
-        <v>52.07</v>
+        <v>50.76</v>
       </c>
       <c r="D85" s="7">
-        <v>54.97</v>
+        <v>60.2</v>
       </c>
       <c r="E85" s="7">
-        <v>49.4</v>
-      </c>
-      <c r="F85" s="8">
-        <v>-3.43</v>
-      </c>
-      <c r="G85" s="8">
-        <v>-6.18</v>
+        <v>50.01</v>
+      </c>
+      <c r="F85" s="10">
+        <v>-1.31</v>
+      </c>
+      <c r="G85" s="10">
+        <v>-2.52</v>
       </c>
       <c r="H85" s="9">
         <v>0</v>
@@ -5678,25 +5685,25 @@
     </row>
     <row r="86" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
-        <v>42278</v>
+        <v>42309</v>
       </c>
       <c r="B86" s="7">
-        <v>50</v>
+        <v>55.5</v>
       </c>
       <c r="C86" s="7">
-        <v>55.5</v>
+        <v>52.07</v>
       </c>
       <c r="D86" s="7">
-        <v>64</v>
+        <v>54.97</v>
       </c>
       <c r="E86" s="7">
-        <v>49.01</v>
+        <v>49.4</v>
       </c>
       <c r="F86" s="10">
-        <v>4.5</v>
+        <v>-3.43</v>
       </c>
       <c r="G86" s="10">
-        <v>8.82</v>
+        <v>-6.18</v>
       </c>
       <c r="H86" s="9">
         <v>0</v>
@@ -5731,25 +5738,25 @@
     </row>
     <row r="87" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
-        <v>42248</v>
-      </c>
-      <c r="B87" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C87" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D87" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E87" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F87" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G87" s="9" t="s">
-        <v>17</v>
+        <v>42278</v>
+      </c>
+      <c r="B87" s="7">
+        <v>50</v>
+      </c>
+      <c r="C87" s="7">
+        <v>55.5</v>
+      </c>
+      <c r="D87" s="7">
+        <v>64</v>
+      </c>
+      <c r="E87" s="7">
+        <v>49.01</v>
+      </c>
+      <c r="F87" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="G87" s="8">
+        <v>8.82</v>
       </c>
       <c r="H87" s="9">
         <v>0</v>
@@ -5784,7 +5791,7 @@
     </row>
     <row r="88" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A88" s="6">
-        <v>42217</v>
+        <v>42248</v>
       </c>
       <c r="B88" s="7" t="s">
         <v>17</v>
@@ -5837,54 +5844,107 @@
     </row>
     <row r="89" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
+        <v>42217</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E89" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F89" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G89" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H89" s="9">
+        <v>0</v>
+      </c>
+      <c r="I89" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J89" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K89" s="9">
+        <v>0</v>
+      </c>
+      <c r="L89" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M89" s="9">
+        <v>0</v>
+      </c>
+      <c r="N89" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O89" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P89" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A90" s="6">
         <v>42186</v>
       </c>
-      <c r="B89" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C89" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D89" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E89" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F89" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G89" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H89" s="9">
-        <v>0</v>
-      </c>
-      <c r="I89" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J89" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="K89" s="9">
-        <v>0</v>
-      </c>
-      <c r="L89" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="M89" s="9">
-        <v>0</v>
-      </c>
-      <c r="N89" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O89" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="P89" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q89" s="9" t="s">
+      <c r="B90" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E90" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F90" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G90" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H90" s="9">
+        <v>0</v>
+      </c>
+      <c r="I90" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J90" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K90" s="9">
+        <v>0</v>
+      </c>
+      <c r="L90" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M90" s="9">
+        <v>0</v>
+      </c>
+      <c r="N90" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O90" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P90" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="9" t="s">
         <v>17</v>
       </c>
     </row>
@@ -5903,7 +5963,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>